--- a/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
@@ -2257,7 +2257,7 @@
         <is>
           <t>寿山村道9号
 4271呎 (4+房)
-(16年-08月)
+(16年-08月-15日)
 $3.88亿
 $90,845/呎</t>
         </is>
@@ -2266,7 +2266,7 @@
         <is>
           <t>寿山村道11A号
 3553呎 (4+房)
-(18年-07月)
+(18年-07月-16日)
 $2.88亿
 $81,002/呎</t>
         </is>
@@ -2275,7 +2275,7 @@
         <is>
           <t>寿山村道11B号
 3602呎 (4+房)
-(21年-06月)
+(21年-06月-09日)
 $2.95亿
 $81,977/呎</t>
         </is>
@@ -2284,7 +2284,7 @@
         <is>
           <t>寿山村道11C号
 3601呎 (4+房)
-(26年-02月)
+(26年-02月-22日)
 $1.80亿
 $49,986/呎</t>
         </is>
@@ -2293,7 +2293,7 @@
         <is>
           <t>寿山村道11D号
 3605呎 (4+房)
-(16年-06月)
+(16年-06月-13日)
 $2.65亿
 $73,444/呎</t>
         </is>
@@ -2302,7 +2302,7 @@
         <is>
           <t>寿山村道11E号
 3606呎 (4+房)
-(13年-12月)
+(13年-12月-16日)
 $2.63亿
 $72,889/呎</t>
         </is>
@@ -2318,7 +2318,7 @@
         <is>
           <t>寿山村道11F号
 3567呎 (4+房)
-(17年-04月)
+(17年-04月-17日)
 $2.83亿
 $79,479/呎</t>
         </is>
@@ -2327,7 +2327,7 @@
         <is>
           <t>寿山村道11G号
 3601呎 (4+房)
-(21年-06月)
+(21年-06月-07日)
 $3.10亿
 $86,123/呎</t>
         </is>
@@ -2336,7 +2336,7 @@
         <is>
           <t>寿山村道15号
 4111呎 (4+房)
-(11年-01月)
+(11年-01月-31日)
 $2.83亿
 $68,791/呎</t>
         </is>
@@ -2345,7 +2345,7 @@
         <is>
           <t>寿山村道17A号
 2989呎 (4+房)
-(12年-04月)
+(12年-04月-26日)
 $2.08亿
 $69,588/呎</t>
         </is>
@@ -2354,7 +2354,7 @@
         <is>
           <t>寿山村道17B号
 2834呎 (4+房)
-(11年-07月)
+(11年-07月-03日)
 $1.88亿
 $66,267/呎</t>
         </is>
@@ -2363,7 +2363,7 @@
         <is>
           <t>寿山村道17C号
 2736呎 (4+房)
-(11年-05月)
+(11年-05月-31日)
 $1.81亿
 $66,082/呎</t>
         </is>
@@ -2379,7 +2379,7 @@
         <is>
           <t>寿山村道17D号
 2893呎 (4+房)
-(12年-04月)
+(12年-04月-19日)
 $1.93亿
 $66,644/呎</t>
         </is>
@@ -2388,7 +2388,7 @@
         <is>
           <t>寿山村道17E号
 2953呎 (4+房)
-(11年-06月)
+(11年-06月-21日)
 $2.05亿
 $69,421/呎</t>
         </is>
@@ -2397,7 +2397,7 @@
         <is>
           <t>寿山村道17F号
 2927呎 (4+房)
-(12年-12月)
+(12年-12月-05日)
 $2.11亿
 $72,087/呎</t>
         </is>
@@ -2406,7 +2406,7 @@
         <is>
           <t>寿山村道17G号
 2927呎 (4+房)
-(16年-10月)
+(16年-10月-31日)
 $2.28亿
 $78,039/呎</t>
         </is>
@@ -2424,7 +2424,7 @@
         <is>
           <t>寿山村道17J号
 2897呎 (4+房)
-(25年-06月)
+(25年-06月-18日)
 $1.29亿
 $44,460/呎</t>
         </is>
@@ -2440,7 +2440,7 @@
         <is>
           <t>寿山村道17K号
 2950呎 (4+房)
-(25年-07月)
+(25年-07月-03日)
 $1.25亿
 $42,372/呎</t>
         </is>
@@ -2449,7 +2449,7 @@
         <is>
           <t>寿山村道17L号
 2948呎 (4+房)
-(25年-08月)
+(25年-08月-27日)
 $1.27亿
 $43,073/呎</t>
         </is>
@@ -2458,7 +2458,7 @@
         <is>
           <t>寿山村道17M号
 2967呎 (4+房)
-(25年-09月)
+(25年-09月-18日)
 $1.34亿
 $45,056/呎</t>
         </is>
@@ -2467,7 +2467,7 @@
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
-(21年-06月)
+(21年-06月-22日)
 $1.95亿
 $70,628/呎</t>
         </is>
@@ -2476,7 +2476,7 @@
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
-(26年-05月)
+(26年-05月-27日)
 $1.51亿
 $55,121/呎</t>
         </is>
@@ -2485,7 +2485,7 @@
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
-(25年-08月)
+(25年-08月-28日)
 $1.17亿
 $43,063/呎</t>
         </is>
@@ -2501,7 +2501,7 @@
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
-(26年-06月)
+(26年-06月-16日)
 $1.83亿
 $65,166/呎</t>
         </is>
@@ -2510,7 +2510,7 @@
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
-(13年-12月)
+(13年-12月-17日)
 $2.30亿
 $71,242/呎</t>
         </is>
@@ -2519,7 +2519,7 @@
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
-(19年-03月)
+(19年-03月-05日)
 $2.40亿
 $74,120/呎</t>
         </is>
@@ -2528,7 +2528,7 @@
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
-(14年-11月)
+(14年-11月-10日)
 $2.38亿
 $73,536/呎</t>
         </is>
@@ -2537,7 +2537,7 @@
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
-(14年-01月)
+(14年-01月-02日)
 $2.31亿
 $71,426/呎</t>
         </is>
@@ -2546,7 +2546,7 @@
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
-(18年-05月)
+(18年-05月-09日)
 $2.62亿
 $81,650/呎</t>
         </is>
@@ -2562,7 +2562,7 @@
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
-(17年-05月)
+(17年-05月-01日)
 $3.77亿
 $89,480/呎</t>
         </is>

--- a/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1333,7 +1324,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17L号</t>
+          <t>寿山村道17M号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1352,7 +1343,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2948</v>
+        <v>2967</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1361,14 +1352,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>126979000</v>
+        <v>133680000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>43073</v>
+        <v>45056</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1379,7 +1370,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17M号</t>
+          <t>寿山村道11A号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1398,7 +1389,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2967</v>
+        <v>3553</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1407,14 +1398,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>133680000</v>
+        <v>287800000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>45056</v>
+        <v>81002</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1425,7 +1416,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11A号</t>
+          <t>寿山村道11B号</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1444,7 +1435,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3553</v>
+        <v>3602</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1453,14 +1444,14 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>287800000</v>
+        <v>295282000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>81002</v>
+        <v>81977</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1471,7 +1462,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11B号</t>
+          <t>寿山村道11C号</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1490,7 +1481,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1499,14 +1490,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>295282000</v>
+        <v>180000000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>81977</v>
+        <v>49986</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1517,7 +1508,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11C号</t>
+          <t>寿山村道11D号</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1536,7 +1527,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3601</v>
+        <v>3605</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1545,14 +1536,14 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>180000000</v>
+        <v>264766200</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>49986</v>
+        <v>73444</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1563,7 +1554,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11D号</t>
+          <t>寿山村道11E号</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1582,7 +1573,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3605</v>
+        <v>3606</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1591,14 +1582,14 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>264766200</v>
+        <v>262836500</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>73444</v>
+        <v>72889</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1609,7 +1600,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11E号</t>
+          <t>寿山村道11F号</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1628,7 +1619,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3606</v>
+        <v>3567</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1637,14 +1628,14 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2013-12-16</t>
+          <t>2017-04-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>262836500</v>
+        <v>283500000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>72889</v>
+        <v>79479</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1655,7 +1646,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11F号</t>
+          <t>寿山村道11G号</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1674,7 +1665,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3567</v>
+        <v>3601</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1683,14 +1674,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2017-04-17</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>283500000</v>
+        <v>310128000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>79479</v>
+        <v>86123</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1701,7 +1692,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11G号</t>
+          <t>寿山村道19A号</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1720,7 +1711,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3601</v>
+        <v>3227</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1729,14 +1720,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2013-12-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>310128000</v>
+        <v>229898800</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>86123</v>
+        <v>71242</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1738,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19A号</t>
+          <t>寿山村道19B号</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1766,7 +1757,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3227</v>
+        <v>3238</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1775,14 +1766,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2013-12-17</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>229898800</v>
+        <v>240000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>71242</v>
+        <v>74120</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1784,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19B号</t>
+          <t>寿山村道19C号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1821,14 +1812,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2014-11-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>240000000</v>
+        <v>238108000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>74120</v>
+        <v>73536</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1839,7 +1830,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19C号</t>
+          <t>寿山村道19D号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1867,14 +1858,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2014-11-10</t>
+          <t>2014-01-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>238108000</v>
+        <v>231278800</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>73536</v>
+        <v>71426</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1885,7 +1876,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19D号</t>
+          <t>寿山村道19E号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1904,7 +1895,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3238</v>
+        <v>3212</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1913,14 +1904,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2014-01-02</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>231278800</v>
+        <v>262260000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>71426</v>
+        <v>81650</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1931,7 +1922,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19E号</t>
+          <t>寿山村道17A号</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1950,7 +1941,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3212</v>
+        <v>2989</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1959,14 +1950,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2012-04-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>262260000</v>
+        <v>208000000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>81650</v>
+        <v>69588</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1968,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17A号</t>
+          <t>寿山村道9号</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1996,7 +1987,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2989</v>
+        <v>4271</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2005,14 +1996,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2012-04-26</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>208000000</v>
+        <v>388000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>69588</v>
+        <v>90845</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2014,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>寿山村道9号</t>
+          <t>寿山村道19F号</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2042,7 +2033,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4271</v>
+        <v>4212</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2051,62 +2042,16 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>388000000</v>
+        <v>376888000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>90845</v>
+        <v>89480</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>寿山村道19F号</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>4212</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>376888000</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>89480</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2127,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2181,7 +2126,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>31 套</t>
+          <t>30 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2196,7 +2141,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>30 套</t>
+          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2447,15 +2392,6 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>寿山村道17L号
-2948呎 (4+房)
-(25年-08月-27日)
-$1.27亿
-$43,073/呎</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
           <t>寿山村道17M号
 2967呎 (4+房)
 (25年-09月-18日)
@@ -2463,7 +2399,7 @@
 $45,056/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
@@ -2472,7 +2408,7 @@
 $70,628/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
@@ -2481,7 +2417,7 @@
 $55,121/呎</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
@@ -2490,14 +2426,7 @@
 $43,063/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
@@ -2506,7 +2435,14 @@
 $65,166/呎</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
@@ -2515,7 +2451,7 @@
 $71,242/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
@@ -2524,7 +2460,7 @@
 $74,120/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
@@ -2533,7 +2469,7 @@
 $73,536/呎</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
@@ -2542,7 +2478,7 @@
 $71,426/呎</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
@@ -2551,14 +2487,7 @@
 $81,650/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
@@ -2567,11 +2496,6 @@
 $89,480/呎</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1333,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17M号</t>
+          <t>寿山村道17L号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1343,7 +1352,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2967</v>
+        <v>2948</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1352,14 +1361,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>133680000</v>
+        <v>126979000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>45056</v>
+        <v>43073</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1370,7 +1379,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11A号</t>
+          <t>寿山村道17M号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1389,7 +1398,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3553</v>
+        <v>2967</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1398,14 +1407,14 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2018-07-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>287800000</v>
+        <v>133680000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>81002</v>
+        <v>45056</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1416,7 +1425,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11B号</t>
+          <t>寿山村道11A号</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1435,7 +1444,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3602</v>
+        <v>3553</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1444,14 +1453,14 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>295282000</v>
+        <v>287800000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>81977</v>
+        <v>81002</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1462,7 +1471,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11C号</t>
+          <t>寿山村道11B号</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1481,7 +1490,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1490,14 +1499,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>180000000</v>
+        <v>295282000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>49986</v>
+        <v>81977</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1517,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11D号</t>
+          <t>寿山村道11C号</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1527,7 +1536,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1536,14 +1545,14 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>264766200</v>
+        <v>180000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>73444</v>
+        <v>49986</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1554,7 +1563,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11E号</t>
+          <t>寿山村道11D号</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1573,7 +1582,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1582,14 +1591,14 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2013-12-16</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>262836500</v>
+        <v>264766200</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>72889</v>
+        <v>73444</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1600,7 +1609,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11F号</t>
+          <t>寿山村道11E号</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1619,7 +1628,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3567</v>
+        <v>3606</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1628,14 +1637,14 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2017-04-17</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>283500000</v>
+        <v>262836500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>79479</v>
+        <v>72889</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1646,7 +1655,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11G号</t>
+          <t>寿山村道11F号</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1665,7 +1674,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3601</v>
+        <v>3567</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1674,14 +1683,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2017-04-17</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>310128000</v>
+        <v>283500000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>86123</v>
+        <v>79479</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1692,7 +1701,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19A号</t>
+          <t>寿山村道11G号</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1711,7 +1720,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3227</v>
+        <v>3601</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1720,14 +1729,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2013-12-17</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>229898800</v>
+        <v>310128000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>71242</v>
+        <v>86123</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1747,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19B号</t>
+          <t>寿山村道19A号</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1757,7 +1766,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3238</v>
+        <v>3227</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1766,14 +1775,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2013-12-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>240000000</v>
+        <v>229898800</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>74120</v>
+        <v>71242</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1793,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19C号</t>
+          <t>寿山村道19B号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1812,14 +1821,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2014-11-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>238108000</v>
+        <v>240000000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>73536</v>
+        <v>74120</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1830,7 +1839,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19D号</t>
+          <t>寿山村道19C号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1858,14 +1867,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2014-01-02</t>
+          <t>2014-11-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>231278800</v>
+        <v>238108000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>71426</v>
+        <v>73536</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1885,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19E号</t>
+          <t>寿山村道19D号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1895,7 +1904,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3212</v>
+        <v>3238</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1904,14 +1913,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2014-01-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>262260000</v>
+        <v>231278800</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>81650</v>
+        <v>71426</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1922,7 +1931,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17A号</t>
+          <t>寿山村道19E号</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1941,7 +1950,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2989</v>
+        <v>3212</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1950,14 +1959,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2012-04-26</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>208000000</v>
+        <v>262260000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>69588</v>
+        <v>81650</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1968,7 +1977,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>寿山村道9号</t>
+          <t>寿山村道17A号</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1987,7 +1996,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4271</v>
+        <v>2989</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -1996,14 +2005,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2012-04-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>388000000</v>
+        <v>208000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>90845</v>
+        <v>69588</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2014,44 +2023,90 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>寿山村道9号</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4271</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2016-08-15</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>388000000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>90845</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>寿山村道19F号</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>4212</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>376888000</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>89480</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2072,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2126,22 +2181,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>31 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>30 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2392,6 +2447,15 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
+          <t>寿山村道17L号
+2948呎 (4+房)
+(25年-08月-27日)
+$1.27亿
+$43,073/呎</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
           <t>寿山村道17M号
 2967呎 (4+房)
 (25年-09月-18日)
@@ -2399,7 +2463,7 @@
 $45,056/呎</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
@@ -2408,7 +2472,7 @@
 $70,628/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
@@ -2417,7 +2481,7 @@
 $55,121/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
@@ -2426,7 +2490,14 @@
 $43,063/呎</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
@@ -2435,14 +2506,7 @@
 $65,166/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
@@ -2451,7 +2515,7 @@
 $71,242/呎</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
@@ -2460,7 +2524,7 @@
 $74,120/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
@@ -2469,7 +2533,7 @@
 $73,536/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
@@ -2478,7 +2542,7 @@
 $71,426/呎</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
@@ -2487,7 +2551,14 @@
 $81,650/呎</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
@@ -2496,6 +2567,11 @@
 $89,480/呎</t>
         </is>
       </c>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
+++ b/港岛-寿臣山及浅水湾-Shouson Peak/Shouson Peak_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2066,52 +2057,6 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>寿山村道19F号</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>4212</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>376888000</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>89480</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -2127,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2181,7 +2126,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>31 套</t>
+          <t>30 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2196,7 +2141,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>30 套</t>
+          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2551,27 +2496,6 @@
 $81,650/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>寿山村道19F号
-4212呎 (4+房)
-(17年-05月-01日)
-$3.77亿
-$89,480/呎</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
